--- a/SlimSat_Data_Dictionary.xlsx
+++ b/SlimSat_Data_Dictionary.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\etapi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b919dd61f447026d/Shared favorites/HSSSI26_SlimSat_Development/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{802722D9-63BF-4B74-B0EF-60F24D6839D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="569" documentId="11_F25DC773A252ABDACC104819219965805BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D6BA4FD-C069-450F-8AED-7D11F5DC107B}"/>
   <bookViews>
-    <workbookView xWindow="8020" yWindow="50" windowWidth="17580" windowHeight="15230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8020" yWindow="50" windowWidth="17580" windowHeight="15230" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SlimSat Data Dictionary" sheetId="1" r:id="rId1"/>
+    <sheet name="Example Commands" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="123">
   <si>
     <t>Eric Tapio</t>
   </si>
@@ -229,6 +230,184 @@
   </si>
   <si>
     <t>Ping Payload Example Commands</t>
+  </si>
+  <si>
+    <t>Example Command</t>
+  </si>
+  <si>
+    <t>$GS01,1,*24</t>
+  </si>
+  <si>
+    <t>$GS01,2,*27</t>
+  </si>
+  <si>
+    <t>$GS01,3,1234*22</t>
+  </si>
+  <si>
+    <t>Register Number</t>
+  </si>
+  <si>
+    <t>$GS01,4,5678*2D</t>
+  </si>
+  <si>
+    <t>$GS01,5,*20</t>
+  </si>
+  <si>
+    <t>$GS01,6,438123456*1B</t>
+  </si>
+  <si>
+    <t>$GS01,7,*22</t>
+  </si>
+  <si>
+    <t>$GS01,8,30000*1E</t>
+  </si>
+  <si>
+    <t>$GS01,9,*2C</t>
+  </si>
+  <si>
+    <t>$GS01,10,4*20</t>
+  </si>
+  <si>
+    <t>$GS01,11,*15</t>
+  </si>
+  <si>
+    <t>$GS01,12,*16</t>
+  </si>
+  <si>
+    <t>$GS01,13,33000*27</t>
+  </si>
+  <si>
+    <t>$GS01,14,*10</t>
+  </si>
+  <si>
+    <t>$GS01,15,1*20</t>
+  </si>
+  <si>
+    <t>$GS01,16,*12</t>
+  </si>
+  <si>
+    <t>$GS01,17,12345*22</t>
+  </si>
+  <si>
+    <t>$GS01,18,*1C</t>
+  </si>
+  <si>
+    <t>$GS01,19,*1D</t>
+  </si>
+  <si>
+    <t>$GS01,20,*17</t>
+  </si>
+  <si>
+    <t>$GS01,21,1*27</t>
+  </si>
+  <si>
+    <t>$GS01,22,*15</t>
+  </si>
+  <si>
+    <t>$GS01,23,5000*11</t>
+  </si>
+  <si>
+    <t>$GS01,24,*13</t>
+  </si>
+  <si>
+    <t>$GS01,25,*12</t>
+  </si>
+  <si>
+    <t>$GS01,30,*16</t>
+  </si>
+  <si>
+    <t>$GS01,31,*17</t>
+  </si>
+  <si>
+    <t>$GS01,32,*14</t>
+  </si>
+  <si>
+    <t>$GS01,33,16*12</t>
+  </si>
+  <si>
+    <t>$GS01,34,*12</t>
+  </si>
+  <si>
+    <t>$GS01,35,*13</t>
+  </si>
+  <si>
+    <t>$GS01,36,*10</t>
+  </si>
+  <si>
+    <t>$GS01,37,*11</t>
+  </si>
+  <si>
+    <t>$GS01,38,*1E</t>
+  </si>
+  <si>
+    <t>$GS01,39,*1F</t>
+  </si>
+  <si>
+    <t>$GS01,2,1000*AA</t>
+  </si>
+  <si>
+    <t>Invalid, incorrect checksum</t>
+  </si>
+  <si>
+    <t>$GS01,66,*15</t>
+  </si>
+  <si>
+    <t>Invalid command ID</t>
+  </si>
+  <si>
+    <t>Incorrect SlimSat ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid, partial message, 2nd half </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid, partial message, 1st half </t>
+  </si>
+  <si>
+    <t>,1000*25</t>
+  </si>
+  <si>
+    <t>$GS01,2,</t>
+  </si>
+  <si>
+    <t>$GS02,2,1000*25</t>
+  </si>
+  <si>
+    <t>Bandwidth Value</t>
+  </si>
+  <si>
+    <t>Spread Factor Value</t>
+  </si>
+  <si>
+    <t>dBm</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>Epoch Time</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>Num Measurements</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>0 -&gt; Not Streaming
+1 -&gt; Stream Data</t>
+  </si>
+  <si>
+    <t>Invalid Commands used in Unit Tests</t>
+  </si>
+  <si>
+    <t>SlimSat System Example Commands</t>
   </si>
 </sst>
 </file>
@@ -508,7 +687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -570,6 +749,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1558,4 +1776,926 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9E38B6-593B-4DF2-9A8D-ECBAAF1B6C37}">
+  <dimension ref="A1:G51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="29.1796875" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="5" spans="1:7" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B7" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B10" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B11" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B13" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="5">
+        <v>7</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B14" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="5">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B15" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5">
+        <v>9</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="5">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B17" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="5">
+        <v>11</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="5">
+        <v>12</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="5">
+        <v>13</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="5">
+        <v>14</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B21" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5">
+        <v>15</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B22" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="5">
+        <v>16</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="31" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="5">
+        <v>17</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="5">
+        <v>18</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B25" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="5">
+        <v>19</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B26" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="5">
+        <v>20</v>
+      </c>
+      <c r="D26" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B27" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="5">
+        <v>21</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B28" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="5">
+        <v>22</v>
+      </c>
+      <c r="D28" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G28" s="31" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B29" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="5">
+        <v>23</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="31" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B30" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="5">
+        <v>24</v>
+      </c>
+      <c r="D30" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="18">
+        <v>25</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G31" s="46" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B33" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G33" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="9">
+        <v>30</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="34" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B35" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="5">
+        <v>31</v>
+      </c>
+      <c r="D35" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B36" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="5">
+        <v>32</v>
+      </c>
+      <c r="D36" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B37" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="5">
+        <v>33</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B38" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="5">
+        <v>34</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B39" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="5">
+        <v>35</v>
+      </c>
+      <c r="D39" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B40" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="5">
+        <v>36</v>
+      </c>
+      <c r="D40" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B41" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" s="5">
+        <v>37</v>
+      </c>
+      <c r="D41" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B42" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" s="5">
+        <v>38</v>
+      </c>
+      <c r="D42" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B43" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="18">
+        <v>39</v>
+      </c>
+      <c r="D43" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B45" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="37" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="G46" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C47" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="D47" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="34" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B48" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="35" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B49" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B50" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E50" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G50" s="35" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51" s="42" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="G51" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>